--- a/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
+++ b/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="修正要望管理表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="修正履歴" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="修正要望_v2.1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +77,25 @@
       <name val="MS Gothic"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="MS Gothic"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -139,6 +157,11 @@
         <fgColor rgb="00E0FFE8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -166,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -218,6 +241,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1454,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1536,10 +1568,774 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>v2.0テスト後の不合格9件・要確認9件を修正要望_v2.1シートに追加</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>PALE BLUE DOT  修正要望管理表  v2.0テスト後（Chrome PC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>管理No.</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>要望内容</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>関連TC</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="inlineStr">
+        <is>
+          <t>対応方針（案）</t>
+        </is>
+      </c>
+      <c r="H2" s="20" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>R-20</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>xボタンで情報パネルを閉じられない</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>TC17</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>#info-panelのz-indexを50以上に引き上げ、クリックイベントが届くよう修正</t>
+        </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t>TC19と同根の可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="50" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>R-21</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>「この惑星を旅する」ボタンが押せない</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>TC19</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>TC17と同根。info-panelへのクリックがブロックされている。TC17の修正で連動解決</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>TC17修正で解決見込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>R-22</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>アルバムを開くと写真がフルスクリーンで表示される（ボタンも非表示）</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>TC27/TC29</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>#album.showがdisplay:flexでなくdisplay:blockの可能性を確認・修正。updateAlbum()のデバッグ</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>アルバム全機能（TC28〜73）がブロック中</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>R-23</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>a星系到達時のボタンテキストが「先へ進む」と表示される</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>TC47</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>"先へ進む" → "プロキシマbへ進む" に文言変更</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr"/>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>R-24</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>「プロキシマbへ進む」を押してもプロキシマbへ着陸できない。a星系に恒星が表示されない</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>TC48</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>choice-aheadのクリックハンドラにProxima bへのナビゲーション処理を追加。buildProximaSystem()でAlpha A/B/Proximaの表示を修正</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>R-23の修正と合わせて対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>R-25</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>大気圏突入中にカメラシェイクが見えない</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>TC53</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>animate()内でreentryShakeをcamera.positionに加算する処理をupdateCamera()の後に移動</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr"/>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>R-26</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>惑星が自転していない（公転停止時に自転も止まる）</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>TC75</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>rotSpeedの適用をsimSpeed(s)から独立させる: m.rotation.y += pd.rotSpeed * dt（sを外す）</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr"/>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>R-27</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>キャッシュ全削除後も写真がリセットされない</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>TC77</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Ctrl+Shift+RではlocalStorageが消えないためpbd_sessionが残る問題。performance.navigationTypeまたは別アプローチで対応を検討</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>v2.0新規TC。対応方針の詳細確認が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>R-28</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>星空の表現がリアルでない</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>TC8</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>星にサイズバリエーション・輝き（glint）・明るさ変化を追加</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>R-29</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>AU表示と光年表示で右上UIに差がない。単位切替をkm/光年の2段階に変更したい</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>TC36/TC37</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>AU単位を廃止しkm↔光年の2段階切替に変更。Uキーのトグル挙動も変更</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr"/>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>R-30</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>宇宙アンビエントドローンが小さすぎてプレイ中に聞こえない</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>TC39/TC40/TC41</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>masterGain・ambientGainを引き上げてユーザーが認識できるレベルに調整</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr"/>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>R-31</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>惑星共鳴音が小さすぎる</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>TC43</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>proxGainをさらに引き上げ。惑星近接時に明確に聴こえるよう調整</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr"/>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>R-32</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>帰還モンタージュ中に惑星が公転で画面外へ消える</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>TC50</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>startReturnJourney()でsimSpeed=0に設定し、startReentry()開始時に復元</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr"/>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>R-33</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>「もう一度旅をする」後も写真が残っている</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>TC56</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>リスタート処理（location.reload()の前）にclearAllPhotos()とlocalStorage.removeItem("pbd_session")を呼ぶ</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr"/>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>R-34</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>F5リロード後に写真・コレクションが消える</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>TC57/TC58</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>loadSavedPhotos()でdataUrlからImageを復元しphotosアレイに追加する処理を追加</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr"/>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>R-35</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Ctrl+ホイールでズーム方向が逆（上に回すとズームアウトする）</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>TC74</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>wheelハンドラのdelta符号を反転: const delta=e.deltaY&gt;0?-1:1;</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>R-36</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>情報パネルを開いても惑星アイコンが自転しない（再クリック後に自転する）</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>TC76</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>showInfoPanel()内でpanel.classList.add("show")の後にdrawIconFrame()を呼ぶよう順序変更</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
+++ b/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
@@ -1486,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1587,6 +1587,28 @@
       <c r="D5" s="18" t="inlineStr">
         <is>
           <t>v2.0テスト後の不合格9件・要確認9件を修正要望_v2.1シートに追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>R-20〜R-36 全18件の修正を実装・ステータスを完了に更新</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1694,7 +1716,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G3" s="18" t="inlineStr">
@@ -1736,7 +1758,7 @@
       </c>
       <c r="F4" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G4" s="18" t="inlineStr">
@@ -1778,7 +1800,7 @@
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G5" s="18" t="inlineStr">
@@ -1820,7 +1842,7 @@
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
@@ -1858,7 +1880,7 @@
       </c>
       <c r="F7" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G7" s="18" t="inlineStr">
@@ -1900,7 +1922,7 @@
       </c>
       <c r="F8" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G8" s="18" t="inlineStr">
@@ -1938,7 +1960,7 @@
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
@@ -1976,7 +1998,7 @@
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -2018,7 +2040,7 @@
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
@@ -2056,7 +2078,7 @@
       </c>
       <c r="F12" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G12" s="18" t="inlineStr">
@@ -2094,7 +2116,7 @@
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr">
@@ -2132,7 +2154,7 @@
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr">
@@ -2170,7 +2192,7 @@
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr">
@@ -2208,7 +2230,7 @@
       </c>
       <c r="F16" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G16" s="18" t="inlineStr">
@@ -2246,7 +2268,7 @@
       </c>
       <c r="F17" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G17" s="18" t="inlineStr">
@@ -2284,7 +2306,7 @@
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G18" s="18" t="inlineStr">
@@ -2322,7 +2344,7 @@
       </c>
       <c r="F19" s="18" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G19" s="18" t="inlineStr">
@@ -2332,6 +2354,7 @@
       </c>
       <c r="H19" s="18" t="inlineStr"/>
     </row>
+    <row r="20"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
+++ b/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
@@ -10,6 +10,7 @@
     <sheet name="修正要望管理表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="修正履歴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="修正要望_v2.1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="修正要望_v2.2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,8 +95,20 @@
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="MS Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -162,6 +175,26 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -189,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -249,6 +282,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1486,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1609,6 +1657,28 @@
       <c r="D6" s="18" t="inlineStr">
         <is>
           <t>R-20〜R-36 全18件の修正を実装・ステータスを完了に更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>v2.1実施の再テスト結果を受け、修正要望_v2.2シートを追加（R-37〜R-51 計15件）</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2354,7 +2424,712 @@
       </c>
       <c r="H19" s="18" t="inlineStr"/>
     </row>
-    <row r="20"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>PALE BLUE DOT  修正要望管理表  v2.1テスト後（Chrome PC  再テスト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>管理No.</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>要望内容</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>関連TC</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t>対応方針（案）</t>
+        </is>
+      </c>
+      <c r="H2" s="23" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>R-37</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>地表ビューでマウスドラッグが効かない（ボタン操作のみ）</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>TC22</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>surface-canvasにmousedown/mousemove/mouseupイベントを追加し、cockpitYaw/cockpitPitchを更新する処理を実装。surface-canvasがid=cの上に重なりメインキャンバスへイベントが届かないことが原因</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>surface-canvas(z-index:55)がWebGLキャンバスを覆っているためイベント非到達</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>R-38</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>惑星自転が視覚的に確認できない</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>TC75</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>rotSpeed適用を pd.rotSpeed * dt * Math.max(1, s) に変更。simSpeed=0（一時停止）時でも1×速度で自転を継続。simSpeed≧1では従来通りsimSpeed倍速</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>v2.1修正でsimSpeedを完全除外したため、低simSpeed時に元より遅く見えなくなった。要再調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>R-39</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>Ctrl+Shift+Rでキャッシュ破棄しても写真がリセットされない</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>TC77</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>performance.getEntriesByType("navigation")[0].transferSizeを参照し、transferSize&gt;0（ハードリロード）検出時にIndexedDBをクリアする。localStorageのpbd_sessionも合わせて削除</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>TC30/TC57/TC58と同根。IndexedDBはブラウザキャッシュクリアで消えない仕様のため根本対応が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>R-40</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>情報パネルの惑星アイコンが常に半分影になっている</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>TC17</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>drawIconFrame()内のCanvas 2D描画にMeshBasicMaterialと同等の均一照明を疑似実装。惑星テクスチャを全面明るく表示（グラデーション一切なし）</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>CSSのcanvas→#c修正でクリック問題は解消済み。但し小アイコン内での影の付き方が問題として残存</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>R-41</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>地表ビュー中にアンビエントサウンドが流れる。土星の情報パネルにリングが表示されない</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>TC21</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>①updateAudio()内でcamState==="surface"判定時にdroneGain/proxGainをlinearRampでフェードアウト。②drawIconFrame()のキャンバスにSaturnのリングをCanvas 2Dで追加描画</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>2つのサブ課題を含む。①はR-42/R-47と同根のサウンド制御系</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>R-42</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>アルバム表示中にアンビエントサウンドが流れる</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>TC27</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>#album-btn・Aキーのクリックハンドラ内でdroneGain.gain.linearRampToValueAtTime(0, t+0.3)を呼ぶ。アルバムを閉じる時に元のゲイン値に復元</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>R-41/R-47と同根のサウンド制御系。アンビエントのON/OFF管理を関数化推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>R-43</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>情報パネル表示中にアルバムを開くと情報パネルが重なって表示される</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>TC29</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>#album-btn・Aキー押下時にdocument.getElementById("info-panel").classList.remove("show")を実行。アルバムを閉じた後、currentPlanetInfoが存在すれば再表示</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>z-index比較: album=30 vs info-panel=50 のため情報パネルが前面に出る</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>R-44</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>旅立ちの日のスロットが最初から埋まっている</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>TC30</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>R-39と同根（Ctrl+Shift+RでIndexedDBが消えず前回セッションの写真が残存）。R-39の修正で連動解決見込み</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>コレクションスロットのハードリセット漏れの可能性も要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>R-45</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>ゲーム起動時にアンビエントサウンドが自動再生される（初回クリックで起動）</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>TC39</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
+        <is>
+          <t>初期状態でミュートアイコン（🔇）を表示し、ミュートボタンを押した時のみinitAudio()を呼ぶ設計に変更。WebAudio APIの自動再生制限への対応</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>ブラウザのAutoplay Policy対応として現状の「初回クリック起動」は合理的。UX改善として対応検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>R-46</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>カメラシェイクが強すぎる（地球が大きく揺れすぎる）</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>TC53</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>reentryShake=intensity*3 → intensity*1.2 に縮小。ランダム加算の係数0.5→0.3に変更。地球がズームしながら細かく振動するよう調整</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>前回×→△に改善済みだが強度が過大。微調整が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>R-47</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>エンディング画面でアンビエントサウンドが流れている</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>TC56</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>showEnding()内でaudioNodes全体のgainをlinearRampToValueAtTime(0, t+2.0)で徐々にフェードアウト</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>R-41/R-42と同根のサウンド制御系。エンディングの雰囲気を壊さないよう長めのフェードを推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>R-48</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>スーパーリロード後も写真・コレクションがリセットされない</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>TC57/TC58</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>R-39と同根。performance.getEntriesByType("navigation")[0].transferSize &gt; 0 をハードリロード判定に使用してR-39修正で連動解決見込み</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>TC77と同根。IndexedDB永続化仕様の根本課題</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>R-49</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>地表描画が科学的にリアルでない（6惑星）</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>TC62〜TC67</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>drawSurfaceView()の各惑星設定（configs）を科学的資料・NASAアーカイブ画像を参考に全面書き直し。大気成分・地形・光源角・特徴的地物を追加</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>6惑星（水星/金星/地球/火星/土星/天王星）が対象。実装工数大のため段階的対応推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>R-50</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>撮影データの名称変更・削除ができない</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>TC72</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>アルバムのphoto-cardに「✏ 名前変更」「🗑 削除」ボタンを追加。IndexedDB上のレコードを更新・削除し、photosアレイとDOMを同期</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>UX改善要望。削除機能はphotoIDをキーにdbDeletePhoto()関数を新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>R-51</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>改善要望</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>情報パネルの惑星アイコンが3D空間の描画より粗い</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>TC76</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t>drawIconFrame()で使用するキャンバスサイズを48×48→128×128に拡大し、CSSでdisplay:blockかつwidth/height:100%で縮小表示。Three.jsのCanvasTextureから高解像度でサンプリング</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>前回修正で自転アニメーションは解消済みだが解像度が低い</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
+++ b/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
@@ -1534,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1679,6 +1679,28 @@
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t>v2.1実施の再テスト結果を受け、修正要望_v2.2シートを追加（R-37〜R-51 計15件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>R-37〜R-51のうち10件実装。地表ドラッグ/自転修正/ハードリロード/アイコン品質/サウンド制御/帰還演出リニューアル</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2550,7 @@
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
@@ -2570,7 +2592,7 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
@@ -2612,7 +2634,7 @@
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
@@ -2654,7 +2676,7 @@
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -2696,7 +2718,7 @@
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
@@ -2738,7 +2760,7 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2780,7 +2802,7 @@
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
@@ -2822,7 +2844,7 @@
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2906,7 +2928,7 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2948,7 +2970,7 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
@@ -2990,7 +3012,7 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
@@ -3116,7 +3138,7 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">

--- a/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
+++ b/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
@@ -1534,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1701,6 +1701,28 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t>R-37〜R-51のうち10件実装。地表ドラッグ/自転修正/ハードリロード/アイコン品質/サウンド制御/帰還演出リニューアル</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>R-45/R-49/R-50 実装完了。全15件のうち計13件が完了（R-45:初期ミュート、R-49:地表描画リアル化6惑星、R-50:写真削除/名前変更機能）</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2908,7 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
@@ -3054,7 +3076,7 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
@@ -3096,7 +3118,7 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">

--- a/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
+++ b/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
@@ -11,6 +11,7 @@
     <sheet name="修正履歴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="修正要望_v2.1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="修正要望_v2.2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="修正要望_v2.3" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,8 +108,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="MS Gothic"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -195,8 +201,18 @@
         <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -218,11 +234,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -298,6 +328,27 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1534,7 +1585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1723,6 +1774,28 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t>R-45/R-49/R-50 実装完了。全15件のうち計13件が完了（R-45:初期ミュート、R-49:地表描画リアル化6惑星、R-50:写真削除/名前変更機能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>追記</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>修正要望_v2.3シート追加（R-52〜R-57）。第3回テスト（2026-04-04）結果を反映。TC17/TC22/TC72/TC75の残存バグと、TC21/TC62〜TC67のR-49再テスト要確認、改善要望書No.20（月の追加）を新規起票</t>
         </is>
       </c>
     </row>
@@ -3180,4 +3253,343 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>PALE BLUE DOT  修正要望管理表  v2.2テスト後（Chrome PC  第3回テスト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>管理No.</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>要望内容</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>関連TC</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>対応方針（案）</t>
+        </is>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>R-52</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>改善要望（再修正）</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>情報パネルの惑星アイコンが常に半影になっている（R-40未解決）</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>TC17</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F3" s="30" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G3" s="29" t="inlineStr">
+        <is>
+          <t>drawIconFrame()内のbrightness(1.6)フィルターでは元テクスチャに焼き込まれたLambertシェーディングのグラデーションを消せない。フィルターをbrightness(3) saturate(0.9) contrast(1.1)の複合指定に強化するか、ictxでdrawImage後にglobalCompositeOperation="screen"で白グラデーションをオーバーレイしシャドウ側を強制的に明るくする。</t>
+        </is>
+      </c>
+      <c r="H3" s="29" t="inlineStr">
+        <is>
+          <t>R-40で対応済とされていたが第3回テストでも△が継続。「常に半分影」の根本原因はCanvasテクスチャ生成時に焼き込まれた暗半球グラデーション。brightness(1.6)では消去不十分</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>R-53</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>バグ（再修正）</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>地表ビューでマウスドラッグが効かない（R-37再修正）</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>TC22</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>surface-ui(z-index:56)がsurface-canvas(z-index:55)の全面を覆っており、surface-canvasへのmousedown/mousemoveイベントが届かない。修正方針：ドラッグリスナーをsurface-canvas→surface-uiに移動。ただしボタン要素(button)上でのmousedownはe.target.tagName==='BUTTON'で除外し、ドラッグ判定はsurface-ui全体で行う。</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>R-37でsurface-canvasにリスナーを追加したが、z-index上位のsurface-uiがイベントを遮断していたため×が継続。ボタン(「宇宙へ戻る」「嵐を止める」)は固有クリックハンドラを持つため影響なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>R-54</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>確認（再テスト要）</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>地表ビュー描画リアル化（R-49対応済、再テスト要）</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>TC21 / TC62〜TC67</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>2026-04-05付けでR-49として6惑星（水星/金星/地球/火星/土星/天王星）のdrawSurfaceView()を全面書き直し済み。第3回テストはR-49実装前日（2026-04-04）に実施されたため△が残存。第4回テストで合否を確認。追加改善が必要な場合は新規Rとして起票。</t>
+        </is>
+      </c>
+      <c r="H5" s="29" t="inlineStr">
+        <is>
+          <t>TC21（地表ビュー表示）は備考なし△のためTC62〜TC67と同一原因（描画品質）と判断。R-49コミット: f41804d</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>R-55</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>ダウンロード時のファイル名がアルバム内表示名と異なる</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>TC72</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>photo-dl-btnのa.download属性が固定値'pale-blue-dot-photo.png'になっている。ph.labelを用いたファイル名生成に変更：
+a.download = (ph.label||'photo').replace(/[\/\?%*:|"&lt;&gt;]/g,'_') + '.png'
+R-50で実装した「名前変更」機能との連携も確認。名前変更後のラベルもダウンロード名に反映させる。</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>R-50（名前変更/削除）では対応済みだがダウンロードファイル名は別件として残存。対応工数は軽微（1行修正）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>R-56</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>バグ（再修正）</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>惑星自転速度がsimSpeed変化に連動せずわかりづらい（R-38再修正）</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>TC75</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>R-38でMath.max(1, simSpeed)を採用した結果、simSpeed=0〜1の全域で自転速度が1×固定になり変化が視認できない。
+修正方針：Math.max(0.5, simSpeed)に変更。
+・simSpeed &lt; 0.5 → 自転速度 = rotSpeed * dt * 0.5（下限固定）
+・simSpeed &gt;= 0.5 → 自転速度 = rotSpeed * dt * simSpeed（線形スケール）
+公転計算はsimSpeedを直接使用するため変更不要。</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>R-38で「Math.max(1,s)」を採用したがsimSpeed=1では変化が見えず×が継続。ユーザー仕様：「時間速度0.5時と同様の速度を下限にし、以下には下げない。公転速度のみ下げる」</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>R-57</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>新機能</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>月の追加（地球周回・公転・自転・情報パネル）</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>新規（改善要望書No.20）</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>改善要望書No.20に対応。実装方針：
+① buildMoon()：SphereGeometry + CanvasTexture（灰色、クレーター模様）でMesh生成
+② 地球のchildren配列に追加し地球基準の相対位置で公転軌道を設定
+③ 自転・公転アニメーションをanimateループに追加（他惑星と同様のrotSpeed/orbitRadiusプロパティ）
+④ クリック時の情報パネル対応（質量：7.35×10²²kg、半径：1737km、平均距離：38.4万km）
+⑤ コレクションスロット追加の要否を別途確認</t>
+        </is>
+      </c>
+      <c r="H8" s="29" t="inlineStr">
+        <is>
+          <t>改善要望書No.20：「地球の周りに月を配置。地球の周りを公転しながら自転する様子を地球などの惑星と同様に表現。公転運動及び自転運動や情報パネルに関する設定も、ほかの惑星とすべて同様とする。」</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
+++ b/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
@@ -1585,7 +1585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1796,6 +1796,28 @@
       <c r="D10" s="26" t="inlineStr">
         <is>
           <t>修正要望_v2.3シート追加（R-52〜R-57）。第3回テスト（2026-04-04）結果を反映。TC17/TC22/TC72/TC75の残存バグと、TC21/TC62〜TC67のR-49再テスト要確認、改善要望書No.20（月の追加）を新規起票</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>R-52/R-53/R-55/R-56 実装完了（アイコン影除去・地表ドラッグ修正・写真ファイル名修正・自転速度下限0.5×修正）</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3373,7 @@
       </c>
       <c r="F3" s="30" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G3" s="29" t="inlineStr">
@@ -3393,7 +3415,7 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G4" s="31" t="inlineStr">
@@ -3477,7 +3499,7 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G6" s="31" t="inlineStr">
@@ -3521,7 +3543,7 @@
       </c>
       <c r="F7" s="30" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G7" s="31" t="inlineStr">

--- a/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
+++ b/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
@@ -1585,7 +1585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1818,6 +1818,28 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t>R-52/R-53/R-55/R-56 実装完了（アイコン影除去・地表ドラッグ修正・写真ファイル名修正・自転速度下限0.5×修正）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>機能追加</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>R-57 月の追加（texMoon・PLANETSエントリ・Three.jsメッシュ・地球周回軌道・情報パネル・目的地メニュー・潮汐固定）</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3611,7 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>未対応</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="G8" s="29" t="inlineStr">

--- a/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
+++ b/docs/PALE_BLUE_DOT_修正要望管理表.xlsx
@@ -12,6 +12,7 @@
     <sheet name="修正要望_v2.1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="修正要望_v2.2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="修正要望_v2.3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="修正要望_v2.4" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,6 +113,17 @@
       <name val="MS Gothic"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="20">
@@ -252,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -350,6 +362,12 @@
     <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1585,7 +1603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1840,6 +1858,26 @@
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t>R-57 月の追加（texMoon・PLANETSエントリ・Three.jsメッシュ・地球周回軌道・情報パネル・目的地メニュー・潮汐固定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>v2.3テスト後の不合格1件(R-58)を修正要望_v2.4シートに追加。情報パネルアイコン描画座標バグ修正完了</t>
         </is>
       </c>
     </row>
@@ -3636,4 +3674,122 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>PALE BLUE DOT  修正要望管理表  v2.3テスト後（Chrome PC  第4回テスト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>管理No.</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>要望内容</t>
+        </is>
+      </c>
+      <c r="D2" s="35" t="inlineStr">
+        <is>
+          <t>関連TC</t>
+        </is>
+      </c>
+      <c r="E2" s="35" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="F2" s="35" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="G2" s="35" t="inlineStr">
+        <is>
+          <t>対応方針（案）</t>
+        </is>
+      </c>
+      <c r="H2" s="35" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>R-58</t>
+        </is>
+      </c>
+      <c r="B3" s="36" t="inlineStr">
+        <is>
+          <t>バグ（再修正）</t>
+        </is>
+      </c>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>情報パネルの惑星アイコンが正しく描画されない（R-52再修正）</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="inlineStr">
+        <is>
+          <t>TC17</t>
+        </is>
+      </c>
+      <c r="E3" s="36" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F3" s="36" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="G3" s="36" t="inlineStr">
+        <is>
+          <t>drawIconFrame()のdrawImage描画先座標が(-58,0)で、クリップ円(中心64,64 半径58)に対してずれていた。座標を(6,6)に修正しテクスチャが円全体をカバーするよう変更。不要なbrightness(2.5)+screen blendフィルタも除去</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>R-40→R-52→R-58。根本原因はdrawImage座標の誤り</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>